--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,9 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0130E74-85F0-4260-B64B-3C188B9B9DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B329515E-084A-4E54-8B8C-54C1BB6A2CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{85126765-781C-418F-98CB-143316E98FFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -71,7 +72,7 @@
     <author>tc={2CD69954-9FBF-4F0C-A085-7745F169BA9F}</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{4E18937C-0B14-4E86-B599-4BF7BA80B225}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{4E18937C-0B14-4E86-B599-4BF7BA80B225}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -79,7 +80,7 @@
     This is fine for winter, but for the summer, this would highly bias the results towards the weekend.</t>
       </text>
     </comment>
-    <comment ref="A4" authorId="1" shapeId="0" xr:uid="{2CD69954-9FBF-4F0C-A085-7745F169BA9F}">
+    <comment ref="B4" authorId="1" shapeId="0" xr:uid="{2CD69954-9FBF-4F0C-A085-7745F169BA9F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -92,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>Annual AF</t>
   </si>
@@ -161,18 +162,6 @@
   </si>
   <si>
     <t>Rainy Days</t>
-  </si>
-  <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Running Total</t>
-  </si>
-  <si>
-    <t>Count</t>
   </si>
   <si>
     <t>AF/year to m3/week</t>
@@ -182,7 +171,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,18 +186,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -237,20 +214,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -268,9 +247,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -292,8 +268,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:P6" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:P6" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:P9" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:P9" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{FADC07E8-CEDF-4B75-BBE4-A01ACB71EDD0}" name="Season"/>
     <tableColumn id="2" xr3:uid="{19D40EF6-9320-45FB-A774-40B56854F6B1}" name="Rainy Days"/>
@@ -310,7 +286,7 @@
     <tableColumn id="13" xr3:uid="{2AE3D243-D71B-48B9-87D2-BFD00350BF9A}" name="Total Replacement Cost ($)"/>
     <tableColumn id="14" xr3:uid="{B5251DEF-3E31-4ABB-B44C-AE5BAB4EED3A}" name="Degree of Flexibility"/>
     <tableColumn id="15" xr3:uid="{2C164AA9-7F5B-49E1-A3E8-CC250E8A10E0}" name="Levelized Cost of Water ($/m3)"/>
-    <tableColumn id="16" xr3:uid="{DD6FED5F-B3AC-4690-ADB6-A1351F19574D}" name="Total OPEX Cost" dataDxfId="1">
+    <tableColumn id="16" xr3:uid="{DD6FED5F-B3AC-4690-ADB6-A1351F19574D}" name="Total OPEX Cost" dataDxfId="0">
       <calculatedColumnFormula>M2+L2+K2+J2+I2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -592,10 +568,10 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D1" dT="2026-08-21T19:08:40.15" personId="{D208FEB8-F7DA-4D83-AAE5-2EEFF5739FC7}" id="{4E18937C-0B14-4E86-B599-4BF7BA80B225}">
+  <threadedComment ref="E1" dT="2026-08-21T19:08:40.15" personId="{D208FEB8-F7DA-4D83-AAE5-2EEFF5739FC7}" id="{4E18937C-0B14-4E86-B599-4BF7BA80B225}">
     <text>This is fine for winter, but for the summer, this would highly bias the results towards the weekend.</text>
   </threadedComment>
-  <threadedComment ref="A4" dT="2026-08-21T19:09:12.49" personId="{D208FEB8-F7DA-4D83-AAE5-2EEFF5739FC7}" id="{2CD69954-9FBF-4F0C-A085-7745F169BA9F}">
+  <threadedComment ref="B4" dT="2026-08-21T19:09:12.49" personId="{D208FEB8-F7DA-4D83-AAE5-2EEFF5739FC7}" id="{2CD69954-9FBF-4F0C-A085-7745F169BA9F}">
     <text>Two Trains on for one day</text>
   </threadedComment>
 </ThreadedComments>
@@ -615,11 +591,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D2">
@@ -644,64 +620,63 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <f>C4/$G$10</f>
         <v>1190.7306933411717</v>
       </c>
       <c r="C4">
         <v>28000</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <f>C5/$G$10</f>
         <v>1798.4286079070769</v>
       </c>
       <c r="C5">
         <v>42290</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <f>C6/$G$10</f>
         <v>2397.9615120043568</v>
       </c>
       <c r="C6">
         <v>56388</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="5"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="D7" s="1"/>
+      <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="D8" s="1"/>
+      <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="1"/>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>8000</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>188119.78330000001</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>80541.55863</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="1"/>
       <c r="G10">
         <f>C10/B10</f>
         <v>23.514972912500003</v>
@@ -711,86 +686,86 @@
       <c r="B11">
         <v>9000</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="F11" s="2"/>
+      <c r="D11" s="3"/>
+      <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <f>C12/$G$10</f>
         <v>9591.8460480174272</v>
       </c>
       <c r="C12">
         <v>225552</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>10000</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>11000</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>258664.69889999999</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>108042.46335199999</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>12000</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>13000</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>14000</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>329209.6164</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>136028.56817899999</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>15000</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>16000</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
@@ -803,11 +778,11 @@
       <c r="C20">
         <v>394716</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>171053.54809522501</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -820,160 +795,218 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E02D5E1-F801-4839-8C05-CA5C31CB2DFA}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="B1:H22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" customWidth="1"/>
+    <col min="7" max="7" width="10.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D1" s="1" t="s">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D2">
-        <v>0</v>
-      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4">
-        <v>28000</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1191</v>
+      </c>
+      <c r="D4" s="3">
+        <v>28006.332369864798</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="3">
+        <v>16720.240035535448</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C5">
-        <v>42290</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1798</v>
+      </c>
+      <c r="D5" s="3">
+        <v>42292.226399718798</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="3">
+        <v>22368.52857086459</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C6">
-        <v>56388</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B10">
+        <v>2398</v>
+      </c>
+      <c r="D6" s="3">
+        <v>56388.904300408598</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="3">
+        <v>28772.571914996501</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C7">
+        <v>3000</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C8">
+        <v>4000</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C9">
+        <v>5000</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C10">
+        <v>6000</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C11">
+        <v>7000</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C12">
         <v>8000</v>
       </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B11">
+      <c r="D12" s="3">
+        <v>188119.78330000001</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12">
+        <f>D12/C12</f>
+        <v>23.514972912500003</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C13">
         <v>9000</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B12">
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C14" s="3">
+        <f>D14/H12</f>
+        <v>9591.8460480174272</v>
+      </c>
+      <c r="D14">
+        <v>225552</v>
+      </c>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C15">
         <v>10000</v>
       </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B13">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C16">
         <v>11000</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C14">
-        <v>225552</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B15">
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C17">
         <v>12000</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B16">
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C18">
         <v>13000</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B17">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C19">
         <v>14000</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B18">
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C20">
         <v>15000</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B19">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C21">
         <v>16000</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
         <v>3</v>
       </c>
-      <c r="C20">
+      <c r="D22">
         <v>394716</v>
       </c>
-      <c r="D20" s="4">
+      <c r="E22" s="3">
         <v>158104.1957609462</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="E1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -1000,56 +1033,56 @@
     <col min="13" max="13" width="25.36328125" customWidth="1"/>
     <col min="14" max="14" width="19.1796875" customWidth="1"/>
     <col min="15" max="15" width="28.6328125" customWidth="1"/>
-    <col min="16" max="16" width="16.26953125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="16.26953125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1099,7 +1132,7 @@
       <c r="O2">
         <v>0.70492795036996803</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="3">
         <f>M2+L2+K2+J2+I2</f>
         <v>158104.1957609462</v>
       </c>
@@ -1150,7 +1183,7 @@
       <c r="O3">
         <v>0.73773470848030298</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="3">
         <f t="shared" ref="P3:P12" si="0">M3+L3+K3+J3+I3</f>
         <v>171053.54809522501</v>
       </c>
@@ -1201,7 +1234,7 @@
       <c r="O4">
         <v>1.0667868110000001</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="3">
         <f t="shared" si="0"/>
         <v>80541.55863</v>
       </c>
@@ -1252,7 +1285,7 @@
       <c r="O5">
         <v>0.88211430199999996</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="3">
         <f t="shared" si="0"/>
         <v>108042.46335199999</v>
       </c>
@@ -1303,43 +1336,178 @@
       <c r="O6">
         <v>0.77806027200000005</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="3">
         <f t="shared" si="0"/>
         <v>136028.56817899999</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="P7" s="4">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>2398</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>56388.904300408598</v>
+      </c>
+      <c r="F7">
+        <v>148904.51312256299</v>
+      </c>
+      <c r="G7">
+        <v>3492.0724412416398</v>
+      </c>
+      <c r="H7">
+        <v>5287.8238927682696</v>
+      </c>
+      <c r="I7">
+        <v>10272.519814514601</v>
+      </c>
+      <c r="J7">
+        <v>4291.8348189990802</v>
+      </c>
+      <c r="K7">
+        <v>4008.2796281577898</v>
+      </c>
+      <c r="L7">
+        <v>8779.8963340099108</v>
+      </c>
+      <c r="M7">
+        <v>1420.0413193151201</v>
+      </c>
+      <c r="N7">
+        <v>7.1856287425149698E-2</v>
+      </c>
+      <c r="O7">
+        <v>2.6406704469603199</v>
+      </c>
+      <c r="P7" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>28772.571914996501</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="P8" s="4">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>1798</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>42292.226399718798</v>
+      </c>
+      <c r="F8">
+        <v>142505.590119726</v>
+      </c>
+      <c r="G8">
+        <v>2685.6739628165201</v>
+      </c>
+      <c r="H8">
+        <v>4056.7859256987999</v>
+      </c>
+      <c r="I8">
+        <v>7708.7043999531998</v>
+      </c>
+      <c r="J8">
+        <v>3463.15238966165</v>
+      </c>
+      <c r="K8">
+        <v>3039.2909147149098</v>
+      </c>
+      <c r="L8">
+        <v>6742.45988851532</v>
+      </c>
+      <c r="M8">
+        <v>1414.9209780195099</v>
+      </c>
+      <c r="N8">
+        <v>3.59281437125748E-2</v>
+      </c>
+      <c r="O8">
+        <v>3.36954571208561</v>
+      </c>
+      <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22368.52857086459</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="P9" s="4">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1191</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>28006.332369864798</v>
+      </c>
+      <c r="F9">
+        <v>136852.18124310201</v>
+      </c>
+      <c r="G9">
+        <v>1795.6766797196899</v>
+      </c>
+      <c r="H9">
+        <v>2651.1746633135699</v>
+      </c>
+      <c r="I9">
+        <v>5102.7220616439199</v>
+      </c>
+      <c r="J9">
+        <v>3562.36888913341</v>
+      </c>
+      <c r="K9">
+        <v>2188.25642240973</v>
+      </c>
+      <c r="L9">
+        <v>4446.8513430332696</v>
+      </c>
+      <c r="M9">
+        <v>1420.0413193151201</v>
+      </c>
+      <c r="N9">
+        <v>7.1856287425149698E-2</v>
+      </c>
+      <c r="O9">
+        <v>4.8864727960722396</v>
+      </c>
+      <c r="P9" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16720.240035535448</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="P10" s="4">
+      <c r="P10" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="P11" s="4">
+      <c r="P11" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="P12" s="4">
+      <c r="P12" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,10 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B329515E-084A-4E54-8B8C-54C1BB6A2CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AE8B90-1AC7-4C73-BBD6-11DE1BC07C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{85126765-781C-418F-98CB-143316E98FFE}"/>
+    <workbookView xWindow="-94" yWindow="-94" windowWidth="33103" windowHeight="17983" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -93,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
   <si>
     <t>Annual AF</t>
   </si>
@@ -214,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -222,6 +221,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -268,8 +268,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:P9" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:P9" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:P16" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:P16" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{FADC07E8-CEDF-4B75-BBE4-A01ACB71EDD0}" name="Season"/>
     <tableColumn id="2" xr3:uid="{19D40EF6-9320-45FB-A774-40B56854F6B1}" name="Rainy Days"/>
@@ -579,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1DDFCB-CD48-4284-8222-18B5894FE623}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
@@ -698,7 +698,7 @@
         <v>225552</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="E12" s="5"/>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -783,6 +783,12 @@
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C21">
+        <f>C20*4/7</f>
+        <v>225552</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1015,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44889D92-5C1B-43B6-BE00-3D23C35CC93C}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" customWidth="1"/>
@@ -1184,7 +1190,7 @@
         <v>0.73773470848030298</v>
       </c>
       <c r="P3" s="3">
-        <f t="shared" ref="P3:P12" si="0">M3+L3+K3+J3+I3</f>
+        <f t="shared" ref="P3:P16" si="0">M3+L3+K3+J3+I3</f>
         <v>171053.54809522501</v>
       </c>
     </row>
@@ -1346,7 +1352,7 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>2398</v>
@@ -1397,7 +1403,7 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>1798</v>
@@ -1448,7 +1454,7 @@
         <v>19</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>1191</v>
@@ -1495,21 +1501,360 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>9000</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>211634.775495949</v>
+      </c>
+      <c r="F10">
+        <v>210256.540792755</v>
+      </c>
+      <c r="G10">
+        <v>14871.657722592799</v>
+      </c>
+      <c r="H10">
+        <v>6315.0305970216004</v>
+      </c>
+      <c r="I10">
+        <v>38197.462944573999</v>
+      </c>
+      <c r="J10">
+        <v>14447.7282003115</v>
+      </c>
+      <c r="K10">
+        <v>14872.6788013735</v>
+      </c>
+      <c r="L10">
+        <v>21186.688319614401</v>
+      </c>
+      <c r="M10">
+        <v>1440.8987193540199</v>
+      </c>
+      <c r="N10">
+        <v>0.215568862275449</v>
+      </c>
+      <c r="O10">
+        <v>0.99348767375321601</v>
+      </c>
       <c r="P10" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>90145.456985227414</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>9000</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>211634.75342465701</v>
+      </c>
+      <c r="F11">
+        <v>211023.73897645701</v>
+      </c>
+      <c r="G11">
+        <v>13979.8948916106</v>
+      </c>
+      <c r="H11">
+        <v>10348.134497098899</v>
+      </c>
+      <c r="I11">
+        <v>38132.388004442699</v>
+      </c>
+      <c r="J11">
+        <v>12409.515456003901</v>
+      </c>
+      <c r="K11">
+        <v>14601.823600419501</v>
+      </c>
+      <c r="L11">
+        <v>24328.029388709601</v>
+      </c>
+      <c r="M11">
+        <v>1420.0413193151201</v>
+      </c>
+      <c r="N11">
+        <v>7.1856287425149698E-2</v>
+      </c>
+      <c r="O11">
+        <v>0.99711288227329198</v>
+      </c>
       <c r="P11" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>90891.797768890829</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>4000</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>94059.890410960099</v>
+      </c>
+      <c r="F12">
+        <v>161889.29285442</v>
+      </c>
+      <c r="G12">
+        <v>5971.5226878267204</v>
+      </c>
+      <c r="H12">
+        <v>4341.2709885715803</v>
+      </c>
+      <c r="I12">
+        <v>17071.648401826398</v>
+      </c>
+      <c r="J12">
+        <v>6365.9688698622604</v>
+      </c>
+      <c r="K12">
+        <v>6586.8993794520802</v>
+      </c>
+      <c r="L12">
+        <v>10312.7936763983</v>
+      </c>
+      <c r="M12">
+        <v>1414.9209780195099</v>
+      </c>
+      <c r="N12">
+        <v>3.59281437125748E-2</v>
+      </c>
+      <c r="O12">
+        <v>1.7211299327173799</v>
+      </c>
       <c r="P12" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>41752.231305558547</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>5000</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>117574.86301369801</v>
+      </c>
+      <c r="F13">
+        <v>171622.562462248</v>
+      </c>
+      <c r="G13">
+        <v>7165.5493259188897</v>
+      </c>
+      <c r="H13">
+        <v>5351.6814382900502</v>
+      </c>
+      <c r="I13">
+        <v>21410.810502291701</v>
+      </c>
+      <c r="J13">
+        <v>7925.0526824229901</v>
+      </c>
+      <c r="K13">
+        <v>8217.4859864430091</v>
+      </c>
+      <c r="L13">
+        <v>12517.2307642089</v>
+      </c>
+      <c r="M13">
+        <v>1425.19885437316</v>
+      </c>
+      <c r="N13">
+        <v>0.107784431137724</v>
+      </c>
+      <c r="O13">
+        <v>1.45968753918303</v>
+      </c>
+      <c r="P13" s="3">
+        <f t="shared" si="0"/>
+        <v>51495.778789739757</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>6000</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>141089.835616439</v>
+      </c>
+      <c r="F14">
+        <v>180851.763366364</v>
+      </c>
+      <c r="G14">
+        <v>9009.9398802506803</v>
+      </c>
+      <c r="H14">
+        <v>6484.3371825203403</v>
+      </c>
+      <c r="I14">
+        <v>25427.472602739599</v>
+      </c>
+      <c r="J14">
+        <v>8599.36997146055</v>
+      </c>
+      <c r="K14">
+        <v>9778.6612025114191</v>
+      </c>
+      <c r="L14">
+        <v>15494.277062771</v>
+      </c>
+      <c r="M14">
+        <v>1425.19885437316</v>
+      </c>
+      <c r="N14">
+        <v>0.107784431137724</v>
+      </c>
+      <c r="O14">
+        <v>1.2818199310829099</v>
+      </c>
+      <c r="P14" s="3">
+        <f t="shared" si="0"/>
+        <v>60724.979693855727</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>7000</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>164604.808219178</v>
+      </c>
+      <c r="F15">
+        <v>190504.78628350099</v>
+      </c>
+      <c r="G15">
+        <v>10032.604456728501</v>
+      </c>
+      <c r="H15">
+        <v>7026.5688957394304</v>
+      </c>
+      <c r="I15">
+        <v>29909.134703197102</v>
+      </c>
+      <c r="J15">
+        <v>10545.884248082401</v>
+      </c>
+      <c r="K15">
+        <v>11438.611452872001</v>
+      </c>
+      <c r="L15">
+        <v>17059.173352467998</v>
+      </c>
+      <c r="M15">
+        <v>1435.62713867346</v>
+      </c>
+      <c r="N15">
+        <v>0.179640718562874</v>
+      </c>
+      <c r="O15">
+        <v>1.15734642471583</v>
+      </c>
+      <c r="P15" s="3">
+        <f t="shared" si="0"/>
+        <v>70388.430895292957</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>8000</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16">
+        <v>188119.780821792</v>
+      </c>
+      <c r="F16">
+        <v>200232.66945339</v>
+      </c>
+      <c r="G16">
+        <v>12151.1741066471</v>
+      </c>
+      <c r="H16">
+        <v>8506.1618324637002</v>
+      </c>
+      <c r="I16">
+        <v>33895.456003932901</v>
+      </c>
+      <c r="J16">
+        <v>11134.1989238396</v>
+      </c>
+      <c r="K16">
+        <v>12993.696059624999</v>
+      </c>
+      <c r="L16">
+        <v>20657.335939110799</v>
+      </c>
+      <c r="M16">
+        <v>1435.62713867346</v>
+      </c>
+      <c r="N16">
+        <v>0.179640718562874</v>
+      </c>
+      <c r="O16">
+        <v>1.06438923423513</v>
+      </c>
+      <c r="P16" s="3">
+        <f t="shared" si="0"/>
+        <v>80116.314065181752</v>
       </c>
     </row>
   </sheetData>

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,9 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AE8B90-1AC7-4C73-BBD6-11DE1BC07C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47938CA3-3BBE-45BA-89AD-A631B6094558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-94" yWindow="-94" windowWidth="33103" windowHeight="17983" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="8430" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -213,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -221,7 +222,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -269,7 +269,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:P16" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:P16" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}"/>
+  <autoFilter ref="A1:P16" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Summer"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{FADC07E8-CEDF-4B75-BBE4-A01ACB71EDD0}" name="Season"/>
     <tableColumn id="2" xr3:uid="{19D40EF6-9320-45FB-A774-40B56854F6B1}" name="Rainy Days"/>
@@ -580,24 +586,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1DDFCB-CD48-4284-8222-18B5894FE623}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" customWidth="1"/>
+    <col min="2" max="2" width="9.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.4609375" customWidth="1"/>
+    <col min="4" max="4" width="9.84375" customWidth="1"/>
+    <col min="5" max="5" width="9.4609375" customWidth="1"/>
+    <col min="6" max="6" width="10.3828125" customWidth="1"/>
     <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D2">
         <v>0</v>
       </c>
@@ -608,7 +614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -616,7 +622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -630,7 +636,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>C5/$G$10</f>
         <v>1798.4286079070769</v>
@@ -641,7 +647,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B6" s="3">
         <f>C6/$G$10</f>
         <v>2397.9615120043568</v>
@@ -651,22 +657,22 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B10">
         <v>8000</v>
       </c>
@@ -682,14 +688,19 @@
         <v>23.514972912500003</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B11">
         <v>9000</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="C11" s="3">
+        <v>211634.775495949</v>
+      </c>
+      <c r="D11" s="3">
+        <v>90145.456985227414</v>
+      </c>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B12" s="3">
         <f>C12/$G$10</f>
         <v>9591.8460480174272</v>
@@ -698,10 +709,9 @@
         <v>225552</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="5"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B13">
         <v>10000</v>
       </c>
@@ -709,7 +719,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B14">
         <v>11000</v>
       </c>
@@ -722,7 +732,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B15">
         <v>12000</v>
       </c>
@@ -730,7 +740,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B16">
         <v>13000</v>
       </c>
@@ -738,7 +748,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B17">
         <v>14000</v>
       </c>
@@ -751,7 +761,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B18">
         <v>15000</v>
       </c>
@@ -759,7 +769,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B19">
         <v>16000</v>
       </c>
@@ -767,7 +777,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -784,7 +794,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C21">
         <f>C20*4/7</f>
         <v>225552</v>
@@ -802,23 +812,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E02D5E1-F801-4839-8C05-CA5C31CB2DFA}">
   <dimension ref="B1:H22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.36328125" customWidth="1"/>
+    <col min="3" max="3" width="9.23046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.4609375" customWidth="1"/>
+    <col min="5" max="5" width="9.84375" customWidth="1"/>
+    <col min="6" max="6" width="9.4609375" customWidth="1"/>
+    <col min="7" max="7" width="10.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.4">
       <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="E2">
         <v>0</v>
       </c>
@@ -829,7 +839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -837,7 +847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -853,7 +863,7 @@
         <v>16720.240035535448</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C5">
         <v>1798</v>
       </c>
@@ -866,7 +876,7 @@
         <v>22368.52857086459</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C6">
         <v>2398</v>
       </c>
@@ -879,7 +889,7 @@
         <v>28772.571914996501</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C7">
         <v>3000</v>
       </c>
@@ -888,21 +898,21 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C8">
         <v>4000</v>
       </c>
       <c r="E8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C9">
         <v>5000</v>
       </c>
       <c r="E9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C10">
         <v>6000</v>
       </c>
@@ -912,14 +922,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C11">
         <v>7000</v>
       </c>
       <c r="E11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C12">
         <v>8000</v>
       </c>
@@ -932,13 +942,13 @@
         <v>23.514972912500003</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C13">
         <v>9000</v>
       </c>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <f>D14/H12</f>
         <v>9591.8460480174272</v>
@@ -948,56 +958,56 @@
       </c>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C15">
         <v>10000</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C16">
         <v>11000</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C17">
         <v>12000</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C18">
         <v>13000</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C19">
         <v>14000</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C20">
         <v>15000</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C21">
         <v>16000</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
         <v>3</v>
       </c>
@@ -1022,27 +1032,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44889D92-5C1B-43B6-BE00-3D23C35CC93C}">
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" customWidth="1"/>
-    <col min="3" max="3" width="22.26953125" customWidth="1"/>
-    <col min="4" max="4" width="28.81640625" customWidth="1"/>
-    <col min="5" max="5" width="26.90625" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="2" width="11.84375" customWidth="1"/>
+    <col min="3" max="3" width="22.23046875" customWidth="1"/>
+    <col min="4" max="4" width="28.84375" customWidth="1"/>
+    <col min="5" max="5" width="26.921875" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="20.08984375" customWidth="1"/>
-    <col min="8" max="8" width="21.54296875" customWidth="1"/>
-    <col min="9" max="9" width="18.453125" customWidth="1"/>
-    <col min="10" max="10" width="18.81640625" customWidth="1"/>
+    <col min="7" max="7" width="20.07421875" customWidth="1"/>
+    <col min="8" max="8" width="21.53515625" customWidth="1"/>
+    <col min="9" max="9" width="18.4609375" customWidth="1"/>
+    <col min="10" max="10" width="18.84375" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="22.54296875" customWidth="1"/>
-    <col min="13" max="13" width="25.36328125" customWidth="1"/>
-    <col min="14" max="14" width="19.1796875" customWidth="1"/>
-    <col min="15" max="15" width="28.6328125" customWidth="1"/>
-    <col min="16" max="16" width="16.26953125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="22.53515625" customWidth="1"/>
+    <col min="13" max="13" width="25.3828125" customWidth="1"/>
+    <col min="14" max="14" width="19.15234375" customWidth="1"/>
+    <col min="15" max="15" width="28.61328125" customWidth="1"/>
+    <col min="16" max="16" width="16.23046875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -1092,7 +1102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1143,7 +1153,7 @@
         <v>158104.1957609462</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1194,7 +1204,7 @@
         <v>171053.54809522501</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1245,7 +1255,7 @@
         <v>80541.55863</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1296,7 +1306,7 @@
         <v>108042.46335199999</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1347,7 +1357,7 @@
         <v>136028.56817899999</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1398,7 +1408,7 @@
         <v>28772.571914996501</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1449,7 +1459,7 @@
         <v>22368.52857086459</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1500,7 +1510,7 @@
         <v>16720.240035535448</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1551,7 +1561,7 @@
         <v>90145.456985227414</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1602,7 +1612,7 @@
         <v>90891.797768890829</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1653,7 +1663,7 @@
         <v>41752.231305558547</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1704,7 +1714,7 @@
         <v>51495.778789739757</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1755,7 +1765,7 @@
         <v>60724.979693855727</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1806,7 +1816,7 @@
         <v>70388.430895292957</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>19</v>
       </c>

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47938CA3-3BBE-45BA-89AD-A631B6094558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EAE0BF-9B17-4A37-81B4-CB54097D2D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="57480" yWindow="8430" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="25">
   <si>
     <t>Annual AF</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>AF/year to m3/week</t>
+  </si>
+  <si>
+    <t>Column1</t>
   </si>
 </sst>
 </file>
@@ -202,7 +205,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -210,11 +213,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -222,11 +236,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -268,17 +288,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:P16" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:P16" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:Q21" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:Q21" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
     <filterColumn colId="0">
       <filters>
         <filter val="Summer"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
-  <tableColumns count="16">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:Q19">
+    <sortCondition ref="D1:D21"/>
+  </sortState>
+  <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{FADC07E8-CEDF-4B75-BBE4-A01ACB71EDD0}" name="Season"/>
     <tableColumn id="2" xr3:uid="{19D40EF6-9320-45FB-A774-40B56854F6B1}" name="Rainy Days"/>
+    <tableColumn id="17" xr3:uid="{81458AAC-294B-492C-8D06-7D9B9E12830A}" name="Total OPEX Cost" dataDxfId="0">
+      <calculatedColumnFormula>N2+M2+L2+K2+J2</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="3" xr3:uid="{1F3F565E-E252-4005-928E-82A03DAD0C98}" name="Annual Production (AF)"/>
     <tableColumn id="4" xr3:uid="{3403EB11-E96C-47DE-93E7-64AE2DF24B9C}" name="Number of Allowed Shutdowns"/>
     <tableColumn id="5" xr3:uid="{3404FD88-9CB1-40B3-9593-EFD338F368D9}" name="Total Water Production (m3)"/>
@@ -292,9 +323,7 @@
     <tableColumn id="13" xr3:uid="{2AE3D243-D71B-48B9-87D2-BFD00350BF9A}" name="Total Replacement Cost ($)"/>
     <tableColumn id="14" xr3:uid="{B5251DEF-3E31-4ABB-B44C-AE5BAB4EED3A}" name="Degree of Flexibility"/>
     <tableColumn id="15" xr3:uid="{2C164AA9-7F5B-49E1-A3E8-CC250E8A10E0}" name="Levelized Cost of Water ($/m3)"/>
-    <tableColumn id="16" xr3:uid="{DD6FED5F-B3AC-4690-ADB6-A1351F19574D}" name="Total OPEX Cost" dataDxfId="0">
-      <calculatedColumnFormula>M2+L2+K2+J2+I2</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="16" xr3:uid="{DD6FED5F-B3AC-4690-ADB6-A1351F19574D}" name="Column1" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -736,7 +765,12 @@
       <c r="B15">
         <v>12000</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="C15" s="3">
+        <v>282179.67123257701</v>
+      </c>
+      <c r="D15" s="3">
+        <v>117856.65704778227</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
@@ -756,7 +790,7 @@
         <v>329209.6164</v>
       </c>
       <c r="D17" s="3">
-        <v>136028.56817899999</v>
+        <v>135947.17095224367</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -765,7 +799,12 @@
       <c r="B18">
         <v>15000</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="C18" s="3">
+        <v>352809.20411343698</v>
+      </c>
+      <c r="D18" s="3">
+        <v>146231.12922675692</v>
+      </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
@@ -773,7 +812,12 @@
       <c r="B19">
         <v>16000</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="C19" s="3">
+        <v>376239.56164383498</v>
+      </c>
+      <c r="D19" s="3">
+        <v>159412.81974307698</v>
+      </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
@@ -781,11 +825,11 @@
       <c r="A20" t="s">
         <v>3</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="3">
         <f>C20/$G$10</f>
         <v>16785.730584030498</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="3">
         <v>394716</v>
       </c>
       <c r="D20" s="3">
@@ -902,21 +946,39 @@
       <c r="C8">
         <v>4000</v>
       </c>
+      <c r="D8" s="3">
+        <v>94059.890410960099</v>
+      </c>
       <c r="E8" s="1"/>
+      <c r="F8" s="3">
+        <v>41752.231305558547</v>
+      </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C9">
         <v>5000</v>
       </c>
+      <c r="D9" s="3">
+        <v>117574.86301369801</v>
+      </c>
       <c r="E9" s="1"/>
+      <c r="F9" s="3">
+        <v>51495.778789739757</v>
+      </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C10">
         <v>6000</v>
       </c>
+      <c r="D10" s="3">
+        <v>141089.835616439</v>
+      </c>
       <c r="E10" s="1"/>
+      <c r="F10" s="3">
+        <v>60724.979693855727</v>
+      </c>
       <c r="G10" s="1"/>
       <c r="H10" t="s">
         <v>23</v>
@@ -926,7 +988,13 @@
       <c r="C11">
         <v>7000</v>
       </c>
+      <c r="D11" s="3">
+        <v>164604.808219178</v>
+      </c>
       <c r="E11" s="1"/>
+      <c r="F11" s="3">
+        <v>70388.430895292957</v>
+      </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.4">
@@ -934,28 +1002,42 @@
         <v>8000</v>
       </c>
       <c r="D12" s="3">
-        <v>188119.78330000001</v>
+        <v>188119.780821792</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="3">
+        <v>80116.314065181752</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12">
         <f>D12/C12</f>
-        <v>23.514972912500003</v>
+        <v>23.514972602724001</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C13">
         <v>9000</v>
       </c>
+      <c r="D13" s="5">
+        <v>211634.75342465701</v>
+      </c>
+      <c r="E13" s="3">
+        <v>85155.50909649636</v>
+      </c>
+      <c r="F13" s="3">
+        <v>90891.797768890829</v>
+      </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <f>D14/H12</f>
-        <v>9591.8460480174272</v>
+        <v>9591.8461743762273</v>
       </c>
       <c r="D14">
         <v>225552</v>
       </c>
+      <c r="E14" s="1"/>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.4">
@@ -990,6 +1072,12 @@
       <c r="C19">
         <v>14000</v>
       </c>
+      <c r="D19" s="3">
+        <v>329240.017626649</v>
+      </c>
+      <c r="E19" s="3">
+        <v>130424.39365381806</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
@@ -1010,6 +1098,9 @@
     <row r="22" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
         <v>3</v>
+      </c>
+      <c r="C22" s="3">
+        <v>16785.730584030498</v>
       </c>
       <c r="D22">
         <v>394716</v>
@@ -1031,28 +1122,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44889D92-5C1B-43B6-BE00-3D23C35CC93C}">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="2" width="11.84375" customWidth="1"/>
-    <col min="3" max="3" width="22.23046875" customWidth="1"/>
-    <col min="4" max="4" width="28.84375" customWidth="1"/>
-    <col min="5" max="5" width="26.921875" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="20.07421875" customWidth="1"/>
-    <col min="8" max="8" width="21.53515625" customWidth="1"/>
-    <col min="9" max="9" width="18.4609375" customWidth="1"/>
-    <col min="10" max="10" width="18.84375" customWidth="1"/>
-    <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="22.53515625" customWidth="1"/>
-    <col min="13" max="13" width="25.3828125" customWidth="1"/>
-    <col min="14" max="14" width="19.15234375" customWidth="1"/>
-    <col min="15" max="15" width="28.61328125" customWidth="1"/>
-    <col min="16" max="16" width="16.23046875" style="3" customWidth="1"/>
+    <col min="2" max="3" width="11.84375" customWidth="1"/>
+    <col min="4" max="4" width="22.23046875" customWidth="1"/>
+    <col min="5" max="5" width="28.84375" customWidth="1"/>
+    <col min="6" max="6" width="26.921875" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="20.07421875" customWidth="1"/>
+    <col min="9" max="9" width="21.53515625" customWidth="1"/>
+    <col min="10" max="10" width="18.4609375" customWidth="1"/>
+    <col min="11" max="11" width="18.84375" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="22.53515625" customWidth="1"/>
+    <col min="14" max="14" width="25.3828125" customWidth="1"/>
+    <col min="15" max="15" width="19.15234375" customWidth="1"/>
+    <col min="16" max="16" width="28.61328125" customWidth="1"/>
+    <col min="17" max="17" width="16.23046875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -1060,811 +1151,1069 @@
         <v>22</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="Q1" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>19</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
+        <f>N2+M2+L2+K2+J2</f>
+        <v>158104.1957609462</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>394716</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>278246.340858232</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>26386.1783186127</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>10787.4639632329</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>71120.000035556499</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>21407.1200065704</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>26993.596007378099</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>37173.642281845699</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>1409.83742959549</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.70492795036996803</v>
       </c>
-      <c r="P2" s="3">
-        <f>M2+L2+K2+J2+I2</f>
-        <v>158104.1957609462</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>21</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
+        <f>N3+M3+L3+K3+J3</f>
+        <v>171053.54809522501</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>10</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>394716</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>291195.69319251098</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>29835.6950167217</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>20287.299599563899</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>71120.000035515404</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>21407.120006458899</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>26993.596007369601</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>50122.994616285599</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>1409.83742959549</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.73773470848030298</v>
       </c>
-      <c r="P3" s="3">
-        <f t="shared" ref="P3:P16" si="0">M3+L3+K3+J3+I3</f>
-        <v>171053.54809522501</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
+        <f>N4+M4+L4+K4+J4</f>
+        <v>80541.55863</v>
+      </c>
+      <c r="D4">
         <v>8000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>10</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>188119.78330000001</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>200683.70370000001</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>13644.59908</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>8296.7277529999992</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>33953.835149999999</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>10359.425139999999</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>12877.13408</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>21941.326830000002</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>1409.83743</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>1.0667868110000001</v>
       </c>
-      <c r="P4" s="3">
-        <f t="shared" si="0"/>
-        <v>80541.55863</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5">
-        <v>11000</v>
+      <c r="C5" s="3">
+        <f>N5+M5+L5+K5+J5</f>
+        <v>90145.456985227414</v>
       </c>
       <c r="D5">
+        <v>9000</v>
+      </c>
+      <c r="E5">
         <v>10</v>
       </c>
-      <c r="E5">
-        <v>258664.69889999999</v>
-      </c>
       <c r="F5">
-        <v>228171.83050000001</v>
+        <v>211634.775495949</v>
       </c>
       <c r="G5">
-        <v>18324.725719999999</v>
+        <v>210256.540792755</v>
       </c>
       <c r="H5">
-        <v>9759.3700439999993</v>
+        <v>14871.657722592799</v>
       </c>
       <c r="I5">
-        <v>46660.582040000001</v>
+        <v>6315.0305970216004</v>
       </c>
       <c r="J5">
-        <v>14174.493689999999</v>
+        <v>38197.462944573999</v>
       </c>
       <c r="K5">
-        <v>17700.676439999999</v>
+        <v>14447.7282003115</v>
       </c>
       <c r="L5">
-        <v>28084.09577</v>
+        <v>14872.6788013735</v>
       </c>
       <c r="M5">
-        <v>1422.6154120000001</v>
+        <v>21186.688319614401</v>
       </c>
       <c r="N5">
-        <v>8.9820359000000002E-2</v>
+        <v>1440.8987193540199</v>
       </c>
       <c r="O5">
-        <v>0.88211430199999996</v>
-      </c>
-      <c r="P5" s="3">
-        <f t="shared" si="0"/>
-        <v>108042.46335199999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+        <v>0.215568862275449</v>
+      </c>
+      <c r="P5">
+        <v>0.99348767375321601</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6">
-        <v>14000</v>
+      <c r="C6" s="3">
+        <f>N6+M6+L6+K6+J6</f>
+        <v>108042.46335199999</v>
       </c>
       <c r="D6">
+        <v>11000</v>
+      </c>
+      <c r="E6">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>329209.6164</v>
-      </c>
       <c r="F6">
-        <v>256144.92360000001</v>
+        <v>258664.69889999999</v>
       </c>
       <c r="G6">
-        <v>23256.219349999999</v>
+        <v>228171.83050000001</v>
       </c>
       <c r="H6">
-        <v>11424.37874</v>
+        <v>18324.725719999999</v>
       </c>
       <c r="I6">
-        <v>59375.347860000002</v>
+        <v>9759.3700439999993</v>
       </c>
       <c r="J6">
-        <v>18011.112300000001</v>
+        <v>46660.582040000001</v>
       </c>
       <c r="K6">
-        <v>22525.88279</v>
+        <v>14174.493689999999</v>
       </c>
       <c r="L6">
-        <v>34680.59809</v>
+        <v>17700.676439999999</v>
       </c>
       <c r="M6">
-        <v>1435.6271389999999</v>
+        <v>28084.09577</v>
       </c>
       <c r="N6">
-        <v>0.179640719</v>
+        <v>1422.6154120000001</v>
       </c>
       <c r="O6">
-        <v>0.77806027200000005</v>
-      </c>
-      <c r="P6" s="3">
-        <f t="shared" si="0"/>
-        <v>136028.56817899999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+        <v>8.9820359000000002E-2</v>
+      </c>
+      <c r="P6">
+        <v>0.88211430199999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>19</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
+        <f>N7+M7+L7+K7+J7</f>
+        <v>28772.571914996501</v>
+      </c>
+      <c r="D7">
         <v>2398</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>10</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>56388.904300408598</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>148904.51312256299</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>3492.0724412416398</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>5287.8238927682696</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>10272.519814514601</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>4291.8348189990802</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>4008.2796281577898</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>8779.8963340099108</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>1420.0413193151201</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>7.1856287425149698E-2</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>2.6406704469603199</v>
       </c>
-      <c r="P7" s="3">
-        <f t="shared" si="0"/>
-        <v>28772.571914996501</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
+        <f>N8+M8+L8+K8+J8</f>
+        <v>22368.52857086459</v>
+      </c>
+      <c r="D8">
         <v>1798</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>10</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>42292.226399718798</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>142505.590119726</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>2685.6739628165201</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>4056.7859256987999</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>7708.7043999531998</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>3463.15238966165</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>3039.2909147149098</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>6742.45988851532</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>1414.9209780195099</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>3.59281437125748E-2</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>3.36954571208561</v>
       </c>
-      <c r="P8" s="3">
-        <f t="shared" si="0"/>
-        <v>22368.52857086459</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>19</v>
       </c>
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
+        <f>N9+M9+L9+K9+J9</f>
+        <v>16720.240035535448</v>
+      </c>
+      <c r="D9">
         <v>1191</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>10</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>28006.332369864798</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>136852.18124310201</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>1795.6766797196899</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>2651.1746633135699</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>5102.7220616439199</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>3562.36888913341</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>2188.25642240973</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>4446.8513430332696</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>1420.0413193151201</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>7.1856287425149698E-2</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>4.8864727960722396</v>
       </c>
-      <c r="P9" s="3">
-        <f t="shared" si="0"/>
-        <v>16720.240035535448</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
-      <c r="C10">
-        <v>9000</v>
+      <c r="C10" s="3">
+        <f>N10+M10+L10+K10+J10</f>
+        <v>117856.65704778227</v>
       </c>
       <c r="D10">
+        <v>12000</v>
+      </c>
+      <c r="E10">
         <v>10</v>
       </c>
-      <c r="E10">
-        <v>211634.775495949</v>
-      </c>
       <c r="F10">
-        <v>210256.540792755</v>
+        <v>282179.67123257701</v>
       </c>
       <c r="G10">
-        <v>14871.657722592799</v>
+        <v>237975.63378803901</v>
       </c>
       <c r="H10">
-        <v>6315.0305970216004</v>
+        <v>19793.405782867099</v>
       </c>
       <c r="I10">
-        <v>38197.462944573999</v>
+        <v>10184.8467366445</v>
       </c>
       <c r="J10">
-        <v>14447.7282003115</v>
+        <v>51100.150850479702</v>
       </c>
       <c r="K10">
-        <v>14872.6788013735</v>
+        <v>15994.396781481701</v>
       </c>
       <c r="L10">
-        <v>21186.688319614401</v>
+        <v>19350.851109684401</v>
       </c>
       <c r="M10">
-        <v>1440.8987193540199</v>
+        <v>29978.252519511701</v>
       </c>
       <c r="N10">
-        <v>0.215568862275449</v>
+        <v>1433.00578662475</v>
       </c>
       <c r="O10">
-        <v>0.99348767375321601</v>
-      </c>
-      <c r="P10" s="3">
-        <f t="shared" si="0"/>
-        <v>90145.456985227414</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+        <v>0.16167664670658599</v>
+      </c>
+      <c r="P10">
+        <v>0.84334790223742195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
-      <c r="C11">
-        <v>9000</v>
+      <c r="C11" s="3">
+        <f>N11+M11+L11+K11+J11</f>
+        <v>41752.231305558547</v>
       </c>
       <c r="D11">
+        <v>4000</v>
+      </c>
+      <c r="E11">
         <v>10</v>
       </c>
-      <c r="E11">
-        <v>211634.75342465701</v>
-      </c>
       <c r="F11">
-        <v>211023.73897645701</v>
+        <v>94059.890410960099</v>
       </c>
       <c r="G11">
-        <v>13979.8948916106</v>
+        <v>161889.29285442</v>
       </c>
       <c r="H11">
-        <v>10348.134497098899</v>
+        <v>5971.5226878267204</v>
       </c>
       <c r="I11">
-        <v>38132.388004442699</v>
+        <v>4341.2709885715803</v>
       </c>
       <c r="J11">
-        <v>12409.515456003901</v>
+        <v>17071.648401826398</v>
       </c>
       <c r="K11">
-        <v>14601.823600419501</v>
+        <v>6365.9688698622604</v>
       </c>
       <c r="L11">
-        <v>24328.029388709601</v>
+        <v>6586.8993794520802</v>
       </c>
       <c r="M11">
-        <v>1420.0413193151201</v>
+        <v>10312.7936763983</v>
       </c>
       <c r="N11">
-        <v>7.1856287425149698E-2</v>
+        <v>1414.9209780195099</v>
       </c>
       <c r="O11">
-        <v>0.99711288227329198</v>
-      </c>
-      <c r="P11" s="3">
-        <f t="shared" si="0"/>
-        <v>90891.797768890829</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+        <v>3.59281437125748E-2</v>
+      </c>
+      <c r="P11">
+        <v>1.7211299327173799</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>19</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
-      <c r="C12">
-        <v>4000</v>
+      <c r="C12" s="3">
+        <f>N12+M12+L12+K12+J12</f>
+        <v>51495.778789739757</v>
       </c>
       <c r="D12">
+        <v>5000</v>
+      </c>
+      <c r="E12">
         <v>10</v>
       </c>
-      <c r="E12">
-        <v>94059.890410960099</v>
-      </c>
       <c r="F12">
-        <v>161889.29285442</v>
+        <v>117574.86301369801</v>
       </c>
       <c r="G12">
-        <v>5971.5226878267204</v>
+        <v>171622.562462248</v>
       </c>
       <c r="H12">
-        <v>4341.2709885715803</v>
+        <v>7165.5493259188897</v>
       </c>
       <c r="I12">
-        <v>17071.648401826398</v>
+        <v>5351.6814382900502</v>
       </c>
       <c r="J12">
-        <v>6365.9688698622604</v>
+        <v>21410.810502291701</v>
       </c>
       <c r="K12">
-        <v>6586.8993794520802</v>
+        <v>7925.0526824229901</v>
       </c>
       <c r="L12">
-        <v>10312.7936763983</v>
+        <v>8217.4859864430091</v>
       </c>
       <c r="M12">
-        <v>1414.9209780195099</v>
+        <v>12517.2307642089</v>
       </c>
       <c r="N12">
-        <v>3.59281437125748E-2</v>
+        <v>1425.19885437316</v>
       </c>
       <c r="O12">
-        <v>1.7211299327173799</v>
-      </c>
-      <c r="P12" s="3">
-        <f t="shared" si="0"/>
-        <v>41752.231305558547</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+        <v>0.107784431137724</v>
+      </c>
+      <c r="P12">
+        <v>1.45968753918303</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
-      <c r="C13">
-        <v>5000</v>
+      <c r="C13" s="3">
+        <f>N13+M13+L13+K13+J13</f>
+        <v>60724.979693855727</v>
       </c>
       <c r="D13">
+        <v>6000</v>
+      </c>
+      <c r="E13">
         <v>10</v>
       </c>
-      <c r="E13">
-        <v>117574.86301369801</v>
-      </c>
       <c r="F13">
-        <v>171622.562462248</v>
+        <v>141089.835616439</v>
       </c>
       <c r="G13">
-        <v>7165.5493259188897</v>
+        <v>180851.763366364</v>
       </c>
       <c r="H13">
-        <v>5351.6814382900502</v>
+        <v>9009.9398802506803</v>
       </c>
       <c r="I13">
-        <v>21410.810502291701</v>
+        <v>6484.3371825203403</v>
       </c>
       <c r="J13">
-        <v>7925.0526824229901</v>
+        <v>25427.472602739599</v>
       </c>
       <c r="K13">
-        <v>8217.4859864430091</v>
+        <v>8599.36997146055</v>
       </c>
       <c r="L13">
-        <v>12517.2307642089</v>
+        <v>9778.6612025114191</v>
       </c>
       <c r="M13">
+        <v>15494.277062771</v>
+      </c>
+      <c r="N13">
         <v>1425.19885437316</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.107784431137724</v>
       </c>
-      <c r="O13">
-        <v>1.45968753918303</v>
-      </c>
-      <c r="P13" s="3">
-        <f t="shared" si="0"/>
-        <v>51495.778789739757</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="P13">
+        <v>1.2818199310829099</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
-      <c r="C14">
-        <v>6000</v>
+      <c r="C14" s="3">
+        <f>N14+M14+L14+K14+J14</f>
+        <v>70388.430895292957</v>
       </c>
       <c r="D14">
+        <v>7000</v>
+      </c>
+      <c r="E14">
         <v>10</v>
       </c>
-      <c r="E14">
-        <v>141089.835616439</v>
-      </c>
       <c r="F14">
-        <v>180851.763366364</v>
+        <v>164604.808219178</v>
       </c>
       <c r="G14">
-        <v>9009.9398802506803</v>
+        <v>190504.78628350099</v>
       </c>
       <c r="H14">
-        <v>6484.3371825203403</v>
+        <v>10032.604456728501</v>
       </c>
       <c r="I14">
-        <v>25427.472602739599</v>
+        <v>7026.5688957394304</v>
       </c>
       <c r="J14">
-        <v>8599.36997146055</v>
+        <v>29909.134703197102</v>
       </c>
       <c r="K14">
-        <v>9778.6612025114191</v>
+        <v>10545.884248082401</v>
       </c>
       <c r="L14">
-        <v>15494.277062771</v>
+        <v>11438.611452872001</v>
       </c>
       <c r="M14">
-        <v>1425.19885437316</v>
+        <v>17059.173352467998</v>
       </c>
       <c r="N14">
-        <v>0.107784431137724</v>
+        <v>1435.62713867346</v>
       </c>
       <c r="O14">
-        <v>1.2818199310829099</v>
-      </c>
-      <c r="P14" s="3">
-        <f t="shared" si="0"/>
-        <v>60724.979693855727</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+        <v>0.179640718562874</v>
+      </c>
+      <c r="P14">
+        <v>1.15734642471583</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
-      <c r="C15">
-        <v>7000</v>
+      <c r="C15" s="3">
+        <f>N15+M15+L15+K15+J15</f>
+        <v>80116.314065181752</v>
       </c>
       <c r="D15">
+        <v>8000</v>
+      </c>
+      <c r="E15">
         <v>10</v>
       </c>
-      <c r="E15">
-        <v>164604.808219178</v>
-      </c>
       <c r="F15">
-        <v>190504.78628350099</v>
+        <v>188119.780821792</v>
       </c>
       <c r="G15">
-        <v>10032.604456728501</v>
+        <v>200232.66945339</v>
       </c>
       <c r="H15">
-        <v>7026.5688957394304</v>
+        <v>12151.1741066471</v>
       </c>
       <c r="I15">
-        <v>29909.134703197102</v>
+        <v>8506.1618324637002</v>
       </c>
       <c r="J15">
-        <v>10545.884248082401</v>
+        <v>33895.456003932901</v>
       </c>
       <c r="K15">
-        <v>11438.611452872001</v>
+        <v>11134.1989238396</v>
       </c>
       <c r="L15">
-        <v>17059.173352467998</v>
+        <v>12993.696059624999</v>
       </c>
       <c r="M15">
+        <v>20657.335939110799</v>
+      </c>
+      <c r="N15">
         <v>1435.62713867346</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.179640718562874</v>
       </c>
-      <c r="O15">
-        <v>1.15734642471583</v>
-      </c>
-      <c r="P15" s="3">
-        <f t="shared" si="0"/>
-        <v>70388.430895292957</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="P15">
+        <v>1.06438923423513</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16">
-        <v>8000</v>
+      <c r="C16" s="3">
+        <f>N16+M16+L16+K16+J16</f>
+        <v>90891.797768890829</v>
       </c>
       <c r="D16">
+        <v>9000</v>
+      </c>
+      <c r="E16">
         <v>10</v>
       </c>
-      <c r="E16">
-        <v>188119.780821792</v>
-      </c>
       <c r="F16">
-        <v>200232.66945339</v>
+        <v>211634.75342465701</v>
       </c>
       <c r="G16">
-        <v>12151.1741066471</v>
+        <v>211023.73897645701</v>
       </c>
       <c r="H16">
-        <v>8506.1618324637002</v>
+        <v>13979.8948916106</v>
       </c>
       <c r="I16">
-        <v>33895.456003932901</v>
+        <v>10348.134497098899</v>
       </c>
       <c r="J16">
-        <v>11134.1989238396</v>
+        <v>38132.388004442699</v>
       </c>
       <c r="K16">
-        <v>12993.696059624999</v>
+        <v>12409.515456003901</v>
       </c>
       <c r="L16">
-        <v>20657.335939110799</v>
+        <v>14601.823600419501</v>
       </c>
       <c r="M16">
-        <v>1435.62713867346</v>
+        <v>24328.029388709601</v>
       </c>
       <c r="N16">
-        <v>0.179640718562874</v>
+        <v>1420.0413193151201</v>
       </c>
       <c r="O16">
-        <v>1.06438923423513</v>
-      </c>
-      <c r="P16" s="3">
-        <f t="shared" si="0"/>
-        <v>80116.314065181752</v>
+        <v>7.1856287425149698E-2</v>
+      </c>
+      <c r="P16">
+        <v>0.99711288227329198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3">
+        <f>N17+M17+L17+K17+J17</f>
+        <v>135947.17095224367</v>
+      </c>
+      <c r="D17">
+        <v>14000</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>329210.46374056302</v>
+      </c>
+      <c r="G17">
+        <v>256066.1476925</v>
+      </c>
+      <c r="H17">
+        <v>23209.551664587099</v>
+      </c>
+      <c r="I17">
+        <v>11406.5894564259</v>
+      </c>
+      <c r="J17">
+        <v>59371.758428007903</v>
+      </c>
+      <c r="K17">
+        <v>18001.101366829</v>
+      </c>
+      <c r="L17">
+        <v>22525.164249769001</v>
+      </c>
+      <c r="M17">
+        <v>34616.141121013003</v>
+      </c>
+      <c r="N17">
+        <v>1433.00578662475</v>
+      </c>
+      <c r="O17">
+        <v>0.16167664670658599</v>
+      </c>
+      <c r="P17">
+        <v>0.77781898176327602</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3">
+        <f>N18+M18+L18+K18+J18</f>
+        <v>146231.12922675692</v>
+      </c>
+      <c r="D18">
+        <v>15000</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>352809.20411343698</v>
+      </c>
+      <c r="G18">
+        <v>266342.21303428401</v>
+      </c>
+      <c r="H18">
+        <v>25570.474362879599</v>
+      </c>
+      <c r="I18">
+        <v>12131.5584602935</v>
+      </c>
+      <c r="J18">
+        <v>63635.191303077299</v>
+      </c>
+      <c r="K18">
+        <v>19311.618858247301</v>
+      </c>
+      <c r="L18">
+        <v>24141.387522905101</v>
+      </c>
+      <c r="M18">
+        <v>37702.032823173198</v>
+      </c>
+      <c r="N18">
+        <v>1440.8987193540199</v>
+      </c>
+      <c r="O18">
+        <v>0.215568862275449</v>
+      </c>
+      <c r="P18">
+        <v>0.75491855067547597</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3">
+        <f>N19+M19+L19+K19+J19</f>
+        <v>159412.81974307698</v>
+      </c>
+      <c r="D19">
+        <v>16000</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
+        <v>376239.56164383498</v>
+      </c>
+      <c r="G19">
+        <v>279542.18685761699</v>
+      </c>
+      <c r="H19">
+        <v>27786.2889118024</v>
+      </c>
+      <c r="I19">
+        <v>16122.056810759999</v>
+      </c>
+      <c r="J19">
+        <v>67830.922645459694</v>
+      </c>
+      <c r="K19">
+        <v>20512.593102821898</v>
+      </c>
+      <c r="L19">
+        <v>25738.3428598918</v>
+      </c>
+      <c r="M19">
+        <v>43908.345722562502</v>
+      </c>
+      <c r="N19">
+        <v>1422.6154123410699</v>
+      </c>
+      <c r="O19">
+        <v>8.9820359281437098E-2</v>
+      </c>
+      <c r="P19">
+        <v>0.74298988026741397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
+        <f>N20+M20+L20+K20+J20</f>
+        <v>85155.50909649636</v>
+      </c>
+      <c r="D20">
+        <v>9000</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>211634.75342469101</v>
+      </c>
+      <c r="G20">
+        <v>205282.292769005</v>
+      </c>
+      <c r="H20">
+        <v>12976.0938250995</v>
+      </c>
+      <c r="I20">
+        <v>5920.7681019027004</v>
+      </c>
+      <c r="J20">
+        <v>38324.958904122599</v>
+      </c>
+      <c r="K20">
+        <v>11995.3830822276</v>
+      </c>
+      <c r="L20">
+        <v>14513.1063287708</v>
+      </c>
+      <c r="M20">
+        <v>18896.861927002199</v>
+      </c>
+      <c r="N20">
+        <v>1425.19885437316</v>
+      </c>
+      <c r="O20">
+        <v>0.107784431137724</v>
+      </c>
+      <c r="P20">
+        <v>0.96998384928330195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3">
+        <f>N21+M21+L21+K21+J21</f>
+        <v>130424.39365381806</v>
+      </c>
+      <c r="D21">
+        <v>14000</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>329240.017626649</v>
+      </c>
+      <c r="G21">
+        <v>250530.167023805</v>
+      </c>
+      <c r="H21">
+        <v>20848.0798472356</v>
+      </c>
+      <c r="I21">
+        <v>8176.7344208997802</v>
+      </c>
+      <c r="J21">
+        <v>59388.995445909903</v>
+      </c>
+      <c r="K21">
+        <v>18034.7176814257</v>
+      </c>
+      <c r="L21">
+        <v>22529.657101452402</v>
+      </c>
+      <c r="M21">
+        <v>29024.8142681354</v>
+      </c>
+      <c r="N21">
+        <v>1446.20915689464</v>
+      </c>
+      <c r="O21">
+        <v>0.25149700598802299</v>
+      </c>
+      <c r="P21">
+        <v>0.76093473943346901</v>
       </c>
     </row>
   </sheetData>

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EAE0BF-9B17-4A37-81B4-CB54097D2D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957FE4D1-DB70-47AD-A099-FAC1C4C9941E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="8430" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>Annual AF</t>
   </si>
@@ -233,12 +233,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -288,11 +288,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:Q21" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:Q21" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:Q24" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:Q24" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Summer"/>
+        <filter val="Winter"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
@@ -301,13 +301,13 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:Q19">
-    <sortCondition ref="D1:D21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q24">
+    <sortCondition ref="D1:D24"/>
   </sortState>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{FADC07E8-CEDF-4B75-BBE4-A01ACB71EDD0}" name="Season"/>
     <tableColumn id="2" xr3:uid="{19D40EF6-9320-45FB-A774-40B56854F6B1}" name="Rainy Days"/>
-    <tableColumn id="17" xr3:uid="{81458AAC-294B-492C-8D06-7D9B9E12830A}" name="Total OPEX Cost" dataDxfId="0">
+    <tableColumn id="17" xr3:uid="{81458AAC-294B-492C-8D06-7D9B9E12830A}" name="Total OPEX Cost" dataDxfId="1">
       <calculatedColumnFormula>N2+M2+L2+K2+J2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{1F3F565E-E252-4005-928E-82A03DAD0C98}" name="Annual Production (AF)"/>
@@ -323,7 +323,7 @@
     <tableColumn id="13" xr3:uid="{2AE3D243-D71B-48B9-87D2-BFD00350BF9A}" name="Total Replacement Cost ($)"/>
     <tableColumn id="14" xr3:uid="{B5251DEF-3E31-4ABB-B44C-AE5BAB4EED3A}" name="Degree of Flexibility"/>
     <tableColumn id="15" xr3:uid="{2C164AA9-7F5B-49E1-A3E8-CC250E8A10E0}" name="Levelized Cost of Water ($/m3)"/>
-    <tableColumn id="16" xr3:uid="{DD6FED5F-B3AC-4690-ADB6-A1351F19574D}" name="Column1" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{DD6FED5F-B3AC-4690-ADB6-A1351F19574D}" name="Column1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -626,11 +626,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D2">
@@ -744,7 +744,12 @@
       <c r="B13">
         <v>10000</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="C13" s="7">
+        <v>235149.72602739499</v>
+      </c>
+      <c r="D13" s="3">
+        <v>99135.784106883366</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
@@ -778,7 +783,12 @@
       <c r="B16">
         <v>13000</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="C16" s="3">
+        <v>305694.64383561601</v>
+      </c>
+      <c r="D16" s="3">
+        <v>126980.73146875472</v>
+      </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
@@ -866,11 +876,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="E2">
@@ -1004,7 +1014,6 @@
       <c r="D12" s="3">
         <v>188119.780821792</v>
       </c>
-      <c r="E12" s="7"/>
       <c r="F12" s="3">
         <v>80116.314065181752</v>
       </c>
@@ -1018,7 +1027,7 @@
       <c r="C13">
         <v>9000</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>211634.75342465701</v>
       </c>
       <c r="E13" s="3">
@@ -1122,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44889D92-5C1B-43B6-BE00-3D23C35CC93C}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.69140625" customWidth="1"/>
@@ -1192,11 +1201,11 @@
       <c r="P1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1247,7 +1256,7 @@
         <v>0.70492795036996803</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1298,7 +1307,7 @@
         <v>0.73773470848030298</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1349,7 +1358,7 @@
         <v>1.0667868110000001</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1400,7 +1409,7 @@
         <v>0.99348767375321601</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1409,46 +1418,46 @@
       </c>
       <c r="C6" s="3">
         <f>N6+M6+L6+K6+J6</f>
-        <v>108042.46335199999</v>
+        <v>99135.784106883366</v>
       </c>
       <c r="D6">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>258664.69889999999</v>
+        <v>235149.72602739499</v>
       </c>
       <c r="G6">
-        <v>228171.83050000001</v>
+        <v>219262.567779392</v>
       </c>
       <c r="H6">
-        <v>18324.725719999999</v>
+        <v>16362.727098568001</v>
       </c>
       <c r="I6">
-        <v>9759.3700439999993</v>
+        <v>9463.2475261001691</v>
       </c>
       <c r="J6">
-        <v>46660.582040000001</v>
+        <v>42544.121004540699</v>
       </c>
       <c r="K6">
-        <v>14174.493689999999</v>
+        <v>13222.943008009999</v>
       </c>
       <c r="L6">
-        <v>17700.676439999999</v>
+        <v>16117.5466152914</v>
       </c>
       <c r="M6">
-        <v>28084.09577</v>
+        <v>25825.974624668099</v>
       </c>
       <c r="N6">
-        <v>1422.6154120000001</v>
+        <v>1425.19885437316</v>
       </c>
       <c r="O6">
-        <v>8.9820359000000002E-2</v>
+        <v>0.107784431137724</v>
       </c>
       <c r="P6">
-        <v>0.88211430199999996</v>
+        <v>0.93243811712477798</v>
       </c>
     </row>
     <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
@@ -1604,7 +1613,7 @@
         <v>4.8864727960722396</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1613,46 +1622,46 @@
       </c>
       <c r="C10" s="3">
         <f>N10+M10+L10+K10+J10</f>
-        <v>117856.65704778227</v>
+        <v>108042.46335199999</v>
       </c>
       <c r="D10">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>282179.67123257701</v>
+        <v>258664.69889999999</v>
       </c>
       <c r="G10">
-        <v>237975.63378803901</v>
+        <v>228171.83050000001</v>
       </c>
       <c r="H10">
-        <v>19793.405782867099</v>
+        <v>18324.725719999999</v>
       </c>
       <c r="I10">
-        <v>10184.8467366445</v>
+        <v>9759.3700439999993</v>
       </c>
       <c r="J10">
-        <v>51100.150850479702</v>
+        <v>46660.582040000001</v>
       </c>
       <c r="K10">
-        <v>15994.396781481701</v>
+        <v>14174.493689999999</v>
       </c>
       <c r="L10">
-        <v>19350.851109684401</v>
+        <v>17700.676439999999</v>
       </c>
       <c r="M10">
-        <v>29978.252519511701</v>
+        <v>28084.09577</v>
       </c>
       <c r="N10">
-        <v>1433.00578662475</v>
+        <v>1422.6154120000001</v>
       </c>
       <c r="O10">
-        <v>0.16167664670658599</v>
+        <v>8.9820359000000002E-2</v>
       </c>
       <c r="P10">
-        <v>0.84334790223742195</v>
+        <v>0.88211430199999996</v>
       </c>
     </row>
     <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
@@ -1961,7 +1970,7 @@
         <v>0.99711288227329198</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1970,37 +1979,37 @@
       </c>
       <c r="C17" s="3">
         <f>N17+M17+L17+K17+J17</f>
-        <v>135947.17095224367</v>
+        <v>117856.65704778227</v>
       </c>
       <c r="D17">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="E17">
         <v>10</v>
       </c>
       <c r="F17">
-        <v>329210.46374056302</v>
+        <v>282179.67123257701</v>
       </c>
       <c r="G17">
-        <v>256066.1476925</v>
+        <v>237975.63378803901</v>
       </c>
       <c r="H17">
-        <v>23209.551664587099</v>
+        <v>19793.405782867099</v>
       </c>
       <c r="I17">
-        <v>11406.5894564259</v>
+        <v>10184.8467366445</v>
       </c>
       <c r="J17">
-        <v>59371.758428007903</v>
+        <v>51100.150850479702</v>
       </c>
       <c r="K17">
-        <v>18001.101366829</v>
+        <v>15994.396781481701</v>
       </c>
       <c r="L17">
-        <v>22525.164249769001</v>
+        <v>19350.851109684401</v>
       </c>
       <c r="M17">
-        <v>34616.141121013003</v>
+        <v>29978.252519511701</v>
       </c>
       <c r="N17">
         <v>1433.00578662475</v>
@@ -2009,10 +2018,10 @@
         <v>0.16167664670658599</v>
       </c>
       <c r="P17">
-        <v>0.77781898176327602</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+        <v>0.84334790223742195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2021,49 +2030,49 @@
       </c>
       <c r="C18" s="3">
         <f>N18+M18+L18+K18+J18</f>
-        <v>146231.12922675692</v>
+        <v>126980.73146875472</v>
       </c>
       <c r="D18">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="E18">
         <v>10</v>
       </c>
       <c r="F18">
-        <v>352809.20411343698</v>
+        <v>305694.64383561601</v>
       </c>
       <c r="G18">
-        <v>266342.21303428401</v>
+        <v>247102.32000570599</v>
       </c>
       <c r="H18">
-        <v>25570.474362879599</v>
+        <v>21131.9353706074</v>
       </c>
       <c r="I18">
-        <v>12131.5584602935</v>
+        <v>10804.733671505701</v>
       </c>
       <c r="J18">
-        <v>63635.191303077299</v>
+        <v>55349.379031353703</v>
       </c>
       <c r="K18">
-        <v>19311.618858247301</v>
+        <v>17302.759297447999</v>
       </c>
       <c r="L18">
-        <v>24141.387522905101</v>
+        <v>20961.530107909999</v>
       </c>
       <c r="M18">
-        <v>37702.032823173198</v>
+        <v>31936.669042113201</v>
       </c>
       <c r="N18">
-        <v>1440.8987193540199</v>
+        <v>1430.39398992981</v>
       </c>
       <c r="O18">
-        <v>0.215568862275449</v>
+        <v>0.14371257485029901</v>
       </c>
       <c r="P18">
-        <v>0.75491855067547597</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+        <v>0.80833055138049104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2072,49 +2081,49 @@
       </c>
       <c r="C19" s="3">
         <f>N19+M19+L19+K19+J19</f>
-        <v>159412.81974307698</v>
+        <v>135947.17095224367</v>
       </c>
       <c r="D19">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="E19">
         <v>10</v>
       </c>
       <c r="F19">
-        <v>376239.56164383498</v>
+        <v>329210.46374056302</v>
       </c>
       <c r="G19">
-        <v>279542.18685761699</v>
+        <v>256066.1476925</v>
       </c>
       <c r="H19">
-        <v>27786.2889118024</v>
+        <v>23209.551664587099</v>
       </c>
       <c r="I19">
-        <v>16122.056810759999</v>
+        <v>11406.5894564259</v>
       </c>
       <c r="J19">
-        <v>67830.922645459694</v>
+        <v>59371.758428007903</v>
       </c>
       <c r="K19">
-        <v>20512.593102821898</v>
+        <v>18001.101366829</v>
       </c>
       <c r="L19">
-        <v>25738.3428598918</v>
+        <v>22525.164249769001</v>
       </c>
       <c r="M19">
-        <v>43908.345722562502</v>
+        <v>34616.141121013003</v>
       </c>
       <c r="N19">
-        <v>1422.6154123410699</v>
+        <v>1433.00578662475</v>
       </c>
       <c r="O19">
-        <v>8.9820359281437098E-2</v>
+        <v>0.16167664670658599</v>
       </c>
       <c r="P19">
-        <v>0.74298988026741397</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+        <v>0.77781898176327602</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2123,49 +2132,49 @@
       </c>
       <c r="C20" s="3">
         <f>N20+M20+L20+K20+J20</f>
-        <v>85155.50909649636</v>
+        <v>75506.612155252791</v>
       </c>
       <c r="D20">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="E20">
         <v>10</v>
       </c>
       <c r="F20">
-        <v>211634.75342469101</v>
+        <v>188119.780821919</v>
       </c>
       <c r="G20">
-        <v>205282.292769005</v>
+        <v>195648.75725253901</v>
       </c>
       <c r="H20">
-        <v>12976.0938250995</v>
+        <v>12161.6977771738</v>
       </c>
       <c r="I20">
-        <v>5920.7681019027004</v>
+        <v>4972.06836104795</v>
       </c>
       <c r="J20">
-        <v>38324.958904122599</v>
+        <v>33895.456003948602</v>
       </c>
       <c r="K20">
-        <v>11995.3830822276</v>
+        <v>10202.532257188101</v>
       </c>
       <c r="L20">
-        <v>14513.1063287708</v>
+        <v>12865.0203262988</v>
       </c>
       <c r="M20">
-        <v>18896.861927002199</v>
+        <v>17133.766138221799</v>
       </c>
       <c r="N20">
-        <v>1425.19885437316</v>
+        <v>1409.83742959549</v>
       </c>
       <c r="O20">
-        <v>0.107784431137724</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>0.96998384928330195</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+        <v>1.0400222475155101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2174,45 +2183,198 @@
       </c>
       <c r="C21" s="3">
         <f>N21+M21+L21+K21+J21</f>
-        <v>130424.39365381806</v>
+        <v>85155.50909649636</v>
       </c>
       <c r="D21">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="E21">
         <v>10</v>
       </c>
       <c r="F21">
+        <v>211634.75342469101</v>
+      </c>
+      <c r="G21">
+        <v>205282.292769005</v>
+      </c>
+      <c r="H21">
+        <v>12976.0938250995</v>
+      </c>
+      <c r="I21">
+        <v>5920.7681019027004</v>
+      </c>
+      <c r="J21">
+        <v>38324.958904122599</v>
+      </c>
+      <c r="K21">
+        <v>11995.3830822276</v>
+      </c>
+      <c r="L21">
+        <v>14513.1063287708</v>
+      </c>
+      <c r="M21">
+        <v>18896.861927002199</v>
+      </c>
+      <c r="N21">
+        <v>1425.19885437316</v>
+      </c>
+      <c r="O21">
+        <v>0.107784431137724</v>
+      </c>
+      <c r="P21">
+        <v>0.96998384928330195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3">
+        <f>N22+M22+L22+K22+J22</f>
+        <v>146231.12922675692</v>
+      </c>
+      <c r="D22">
+        <v>15000</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>352809.20411343698</v>
+      </c>
+      <c r="G22">
+        <v>266342.21303428401</v>
+      </c>
+      <c r="H22">
+        <v>25570.474362879599</v>
+      </c>
+      <c r="I22">
+        <v>12131.5584602935</v>
+      </c>
+      <c r="J22">
+        <v>63635.191303077299</v>
+      </c>
+      <c r="K22">
+        <v>19311.618858247301</v>
+      </c>
+      <c r="L22">
+        <v>24141.387522905101</v>
+      </c>
+      <c r="M22">
+        <v>37702.032823173198</v>
+      </c>
+      <c r="N22">
+        <v>1440.8987193540199</v>
+      </c>
+      <c r="O22">
+        <v>0.215568862275449</v>
+      </c>
+      <c r="P22">
+        <v>0.75491855067547597</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3">
+        <f>N23+M23+L23+K23+J23</f>
+        <v>159412.81974307698</v>
+      </c>
+      <c r="D23">
+        <v>16000</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>376239.56164383498</v>
+      </c>
+      <c r="G23">
+        <v>279542.18685761699</v>
+      </c>
+      <c r="H23">
+        <v>27786.2889118024</v>
+      </c>
+      <c r="I23">
+        <v>16122.056810759999</v>
+      </c>
+      <c r="J23">
+        <v>67830.922645459694</v>
+      </c>
+      <c r="K23">
+        <v>20512.593102821898</v>
+      </c>
+      <c r="L23">
+        <v>25738.3428598918</v>
+      </c>
+      <c r="M23">
+        <v>43908.345722562502</v>
+      </c>
+      <c r="N23">
+        <v>1422.6154123410699</v>
+      </c>
+      <c r="O23">
+        <v>8.9820359281437098E-2</v>
+      </c>
+      <c r="P23">
+        <v>0.74298988026741397</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3">
+        <f>N24+M24+L24+K24+J24</f>
+        <v>130424.39365381806</v>
+      </c>
+      <c r="D24">
+        <v>14000</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+      <c r="F24">
         <v>329240.017626649</v>
       </c>
-      <c r="G21">
+      <c r="G24">
         <v>250530.167023805</v>
       </c>
-      <c r="H21">
+      <c r="H24">
         <v>20848.0798472356</v>
       </c>
-      <c r="I21">
+      <c r="I24">
         <v>8176.7344208997802</v>
       </c>
-      <c r="J21">
+      <c r="J24">
         <v>59388.995445909903</v>
       </c>
-      <c r="K21">
+      <c r="K24">
         <v>18034.7176814257</v>
       </c>
-      <c r="L21">
+      <c r="L24">
         <v>22529.657101452402</v>
       </c>
-      <c r="M21">
+      <c r="M24">
         <v>29024.8142681354</v>
       </c>
-      <c r="N21">
+      <c r="N24">
         <v>1446.20915689464</v>
       </c>
-      <c r="O21">
+      <c r="O24">
         <v>0.25149700598802299</v>
       </c>
-      <c r="P21">
+      <c r="P24">
         <v>0.76093473943346901</v>
       </c>
     </row>

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,10 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957FE4D1-DB70-47AD-A099-FAC1C4C9941E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14E49BC-EB75-4A27-B469-C3E5636FE192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="57480" yWindow="8430" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -93,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
   <si>
     <t>Annual AF</t>
   </si>
@@ -167,7 +166,10 @@
     <t>AF/year to m3/week</t>
   </si>
   <si>
-    <t>Column1</t>
+    <t>Flexible?</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -228,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -238,7 +240,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -290,11 +291,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:Q24" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:Q24" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Winter"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="1">
       <filters>
         <filter val="0"/>
@@ -323,7 +319,7 @@
     <tableColumn id="13" xr3:uid="{2AE3D243-D71B-48B9-87D2-BFD00350BF9A}" name="Total Replacement Cost ($)"/>
     <tableColumn id="14" xr3:uid="{B5251DEF-3E31-4ABB-B44C-AE5BAB4EED3A}" name="Degree of Flexibility"/>
     <tableColumn id="15" xr3:uid="{2C164AA9-7F5B-49E1-A3E8-CC250E8A10E0}" name="Levelized Cost of Water ($/m3)"/>
-    <tableColumn id="16" xr3:uid="{DD6FED5F-B3AC-4690-ADB6-A1351F19574D}" name="Column1" dataDxfId="0"/>
+    <tableColumn id="16" xr3:uid="{DD6FED5F-B3AC-4690-ADB6-A1351F19574D}" name="Flexible?" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -744,7 +740,7 @@
       <c r="B13">
         <v>10000</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="4">
         <v>235149.72602739499</v>
       </c>
       <c r="D13" s="3">
@@ -1213,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3">
-        <f>N2+M2+L2+K2+J2</f>
+        <f t="shared" ref="C2:C24" si="0">N2+M2+L2+K2+J2</f>
         <v>158104.1957609462</v>
       </c>
       <c r="D2">
@@ -1255,8 +1251,11 @@
       <c r="P2">
         <v>0.70492795036996803</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+      <c r="Q2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1264,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="3">
-        <f>N3+M3+L3+K3+J3</f>
+        <f t="shared" si="0"/>
         <v>171053.54809522501</v>
       </c>
       <c r="D3">
@@ -1306,8 +1305,11 @@
       <c r="P3">
         <v>0.73773470848030298</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+      <c r="Q3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1315,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <f>N4+M4+L4+K4+J4</f>
+        <f t="shared" si="0"/>
         <v>80541.55863</v>
       </c>
       <c r="D4">
@@ -1357,8 +1359,11 @@
       <c r="P4">
         <v>1.0667868110000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+      <c r="Q4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1366,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <f>N5+M5+L5+K5+J5</f>
+        <f t="shared" si="0"/>
         <v>90145.456985227414</v>
       </c>
       <c r="D5">
@@ -1408,8 +1413,11 @@
       <c r="P5">
         <v>0.99348767375321601</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+      <c r="Q5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1417,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <f>N6+M6+L6+K6+J6</f>
+        <f t="shared" si="0"/>
         <v>99135.784106883366</v>
       </c>
       <c r="D6">
@@ -1458,6 +1466,9 @@
       </c>
       <c r="P6">
         <v>0.93243811712477798</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
@@ -1468,7 +1479,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="3">
-        <f>N7+M7+L7+K7+J7</f>
+        <f t="shared" si="0"/>
         <v>28772.571914996501</v>
       </c>
       <c r="D7">
@@ -1519,7 +1530,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="3">
-        <f>N8+M8+L8+K8+J8</f>
+        <f t="shared" si="0"/>
         <v>22368.52857086459</v>
       </c>
       <c r="D8">
@@ -1570,7 +1581,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="3">
-        <f>N9+M9+L9+K9+J9</f>
+        <f t="shared" si="0"/>
         <v>16720.240035535448</v>
       </c>
       <c r="D9">
@@ -1613,7 +1624,7 @@
         <v>4.8864727960722396</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1621,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="3">
-        <f>N10+M10+L10+K10+J10</f>
+        <f t="shared" si="0"/>
         <v>108042.46335199999</v>
       </c>
       <c r="D10">
@@ -1662,6 +1673,9 @@
       </c>
       <c r="P10">
         <v>0.88211430199999996</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
@@ -1672,7 +1686,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="3">
-        <f>N11+M11+L11+K11+J11</f>
+        <f t="shared" si="0"/>
         <v>41752.231305558547</v>
       </c>
       <c r="D11">
@@ -1723,7 +1737,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="3">
-        <f>N12+M12+L12+K12+J12</f>
+        <f t="shared" si="0"/>
         <v>51495.778789739757</v>
       </c>
       <c r="D12">
@@ -1774,7 +1788,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="3">
-        <f>N13+M13+L13+K13+J13</f>
+        <f t="shared" si="0"/>
         <v>60724.979693855727</v>
       </c>
       <c r="D13">
@@ -1825,7 +1839,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="3">
-        <f>N14+M14+L14+K14+J14</f>
+        <f t="shared" si="0"/>
         <v>70388.430895292957</v>
       </c>
       <c r="D14">
@@ -1876,7 +1890,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="3">
-        <f>N15+M15+L15+K15+J15</f>
+        <f t="shared" si="0"/>
         <v>80116.314065181752</v>
       </c>
       <c r="D15">
@@ -1927,7 +1941,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="3">
-        <f>N16+M16+L16+K16+J16</f>
+        <f t="shared" si="0"/>
         <v>90891.797768890829</v>
       </c>
       <c r="D16">
@@ -1970,7 +1984,7 @@
         <v>0.99711288227329198</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1978,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="3">
-        <f>N17+M17+L17+K17+J17</f>
+        <f t="shared" si="0"/>
         <v>117856.65704778227</v>
       </c>
       <c r="D17">
@@ -2020,8 +2034,11 @@
       <c r="P17">
         <v>0.84334790223742195</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="Q17" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2029,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="3">
-        <f>N18+M18+L18+K18+J18</f>
+        <f t="shared" si="0"/>
         <v>126980.73146875472</v>
       </c>
       <c r="D18">
@@ -2071,8 +2088,11 @@
       <c r="P18">
         <v>0.80833055138049104</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="Q18" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2080,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="3">
-        <f>N19+M19+L19+K19+J19</f>
+        <f t="shared" si="0"/>
         <v>135947.17095224367</v>
       </c>
       <c r="D19">
@@ -2122,8 +2142,11 @@
       <c r="P19">
         <v>0.77781898176327602</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q19" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2131,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="3">
-        <f>N20+M20+L20+K20+J20</f>
+        <f t="shared" si="0"/>
         <v>75506.612155252791</v>
       </c>
       <c r="D20">
@@ -2173,8 +2196,11 @@
       <c r="P20">
         <v>1.0400222475155101</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q20" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2182,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="3">
-        <f>N21+M21+L21+K21+J21</f>
+        <f t="shared" si="0"/>
         <v>85155.50909649636</v>
       </c>
       <c r="D21">
@@ -2224,8 +2250,11 @@
       <c r="P21">
         <v>0.96998384928330195</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="Q21" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2233,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="3">
-        <f>N22+M22+L22+K22+J22</f>
+        <f t="shared" si="0"/>
         <v>146231.12922675692</v>
       </c>
       <c r="D22">
@@ -2275,8 +2304,11 @@
       <c r="P22">
         <v>0.75491855067547597</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="Q22" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2284,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="3">
-        <f>N23+M23+L23+K23+J23</f>
+        <f t="shared" si="0"/>
         <v>159412.81974307698</v>
       </c>
       <c r="D23">
@@ -2326,8 +2358,11 @@
       <c r="P23">
         <v>0.74298988026741397</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q23" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2335,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="3">
-        <f>N24+M24+L24+K24+J24</f>
+        <f t="shared" si="0"/>
         <v>130424.39365381806</v>
       </c>
       <c r="D24">
@@ -2376,6 +2411,9 @@
       </c>
       <c r="P24">
         <v>0.76093473943346901</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14E49BC-EB75-4A27-B469-C3E5636FE192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2565499F-06C5-4BAA-9BC0-DD86E5B7A389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
+    <workbookView xWindow="57480" yWindow="8430" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="27">
   <si>
     <t>Annual AF</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -289,8 +292,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:Q24" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:Q24" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:Q33" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:Q33" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
     <filterColumn colId="1">
       <filters>
         <filter val="0"/>
@@ -1127,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44889D92-5C1B-43B6-BE00-3D23C35CC93C}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.69140625" customWidth="1"/>
@@ -2416,6 +2419,492 @@
         <v>25</v>
       </c>
     </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3">
+        <f t="shared" ref="C25:C33" si="1">N25+M25+L25+K25+J25</f>
+        <v>81475.122661244794</v>
+      </c>
+      <c r="D25">
+        <v>8000</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>188119.780842915</v>
+      </c>
+      <c r="G25">
+        <v>201617.267758531</v>
+      </c>
+      <c r="H25">
+        <v>13751.620935814901</v>
+      </c>
+      <c r="I25">
+        <v>9350.6556949398891</v>
+      </c>
+      <c r="J25">
+        <v>33895.456009555302</v>
+      </c>
+      <c r="K25">
+        <v>10202.5322632261</v>
+      </c>
+      <c r="L25">
+        <v>12865.0203281131</v>
+      </c>
+      <c r="M25">
+        <v>23102.276630754801</v>
+      </c>
+      <c r="N25">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.0717494293005001</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>120337.96252123939</v>
+      </c>
+      <c r="D26">
+        <v>9000</v>
+      </c>
+      <c r="E26">
+        <v>10</v>
+      </c>
+      <c r="F26">
+        <v>279720</v>
+      </c>
+      <c r="G26">
+        <v>240480.10761852501</v>
+      </c>
+      <c r="H26">
+        <v>20374.4461607105</v>
+      </c>
+      <c r="I26">
+        <v>13853.958930933501</v>
+      </c>
+      <c r="J26">
+        <v>50400</v>
+      </c>
+      <c r="K26">
+        <v>15170.3999999999</v>
+      </c>
+      <c r="L26">
+        <v>19129.32</v>
+      </c>
+      <c r="M26">
+        <v>34228.405091644003</v>
+      </c>
+      <c r="N26">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0.85971724445347397</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>120337.96252123939</v>
+      </c>
+      <c r="D27">
+        <v>10000</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>279720</v>
+      </c>
+      <c r="G27">
+        <v>240480.10761852501</v>
+      </c>
+      <c r="H27">
+        <v>20374.4461607105</v>
+      </c>
+      <c r="I27">
+        <v>13853.958930933501</v>
+      </c>
+      <c r="J27">
+        <v>50400</v>
+      </c>
+      <c r="K27">
+        <v>15170.3999999999</v>
+      </c>
+      <c r="L27">
+        <v>19129.32</v>
+      </c>
+      <c r="M27">
+        <v>34228.405091644003</v>
+      </c>
+      <c r="N27">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0.85971724445347397</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>120337.96252123939</v>
+      </c>
+      <c r="D28">
+        <v>11000</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>279720</v>
+      </c>
+      <c r="G28">
+        <v>240480.10761852501</v>
+      </c>
+      <c r="H28">
+        <v>20374.4461607105</v>
+      </c>
+      <c r="I28">
+        <v>13853.958930933501</v>
+      </c>
+      <c r="J28">
+        <v>50400</v>
+      </c>
+      <c r="K28">
+        <v>15170.3999999999</v>
+      </c>
+      <c r="L28">
+        <v>19129.32</v>
+      </c>
+      <c r="M28">
+        <v>34228.405091644003</v>
+      </c>
+      <c r="N28">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0.85971724445347397</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>121509.10762980059</v>
+      </c>
+      <c r="D29">
+        <v>12000</v>
+      </c>
+      <c r="E29">
+        <v>10</v>
+      </c>
+      <c r="F29">
+        <v>282179.67123287602</v>
+      </c>
+      <c r="G29">
+        <v>241651.25272708701</v>
+      </c>
+      <c r="H29">
+        <v>20628.2321749736</v>
+      </c>
+      <c r="I29">
+        <v>14026.525144076701</v>
+      </c>
+      <c r="J29">
+        <v>50843.184005923598</v>
+      </c>
+      <c r="K29">
+        <v>15303.798385783</v>
+      </c>
+      <c r="L29">
+        <v>19297.5304894482</v>
+      </c>
+      <c r="M29">
+        <v>34654.757319050303</v>
+      </c>
+      <c r="N29">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0.85637371278832397</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>160240.68755374721</v>
+      </c>
+      <c r="D30">
+        <v>13000</v>
+      </c>
+      <c r="E30">
+        <v>10</v>
+      </c>
+      <c r="F30">
+        <v>372960.01384574</v>
+      </c>
+      <c r="G30">
+        <v>280382.83265103301</v>
+      </c>
+      <c r="H30">
+        <v>27320.699397881199</v>
+      </c>
+      <c r="I30">
+        <v>18577.186526806599</v>
+      </c>
+      <c r="J30">
+        <v>67200.002496512097</v>
+      </c>
+      <c r="K30">
+        <v>20227.200755707701</v>
+      </c>
+      <c r="L30">
+        <v>25505.7609472441</v>
+      </c>
+      <c r="M30">
+        <v>45897.885924687798</v>
+      </c>
+      <c r="N30">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0.75177719391388198</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>160240.68755374721</v>
+      </c>
+      <c r="D31">
+        <v>14000</v>
+      </c>
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31">
+        <v>372960.01384574</v>
+      </c>
+      <c r="G31">
+        <v>280382.83265103301</v>
+      </c>
+      <c r="H31">
+        <v>27320.699397881199</v>
+      </c>
+      <c r="I31">
+        <v>18577.186526806599</v>
+      </c>
+      <c r="J31">
+        <v>67200.002496512097</v>
+      </c>
+      <c r="K31">
+        <v>20227.200755707701</v>
+      </c>
+      <c r="L31">
+        <v>25505.7609472441</v>
+      </c>
+      <c r="M31">
+        <v>45897.885924687798</v>
+      </c>
+      <c r="N31">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0.75177719391388198</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>160240.68755374721</v>
+      </c>
+      <c r="D32">
+        <v>15000</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <v>372960.01384574</v>
+      </c>
+      <c r="G32">
+        <v>280382.83265103301</v>
+      </c>
+      <c r="H32">
+        <v>27320.699397881199</v>
+      </c>
+      <c r="I32">
+        <v>18577.186526806599</v>
+      </c>
+      <c r="J32">
+        <v>67200.002496512097</v>
+      </c>
+      <c r="K32">
+        <v>20227.200755707701</v>
+      </c>
+      <c r="L32">
+        <v>25505.7609472441</v>
+      </c>
+      <c r="M32">
+        <v>45897.885924687798</v>
+      </c>
+      <c r="N32">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0.75177719391388198</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>161854.2162878394</v>
+      </c>
+      <c r="D33">
+        <v>16000</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33">
+        <v>376239.56166412297</v>
+      </c>
+      <c r="G33">
+        <v>281996.36138512503</v>
+      </c>
+      <c r="H33">
+        <v>27690.037368097801</v>
+      </c>
+      <c r="I33">
+        <v>18828.324302187499</v>
+      </c>
+      <c r="J33">
+        <v>67790.912013336099</v>
+      </c>
+      <c r="K33">
+        <v>20405.064520267199</v>
+      </c>
+      <c r="L33">
+        <v>25730.040654355202</v>
+      </c>
+      <c r="M33">
+        <v>46518.361670285398</v>
+      </c>
+      <c r="N33">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0.74951278418953005</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2565499F-06C5-4BAA-9BC0-DD86E5B7A389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC3565F-11BF-4838-AF9A-FB0F5E3F0EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="8430" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
+    <workbookView xWindow="-6375" yWindow="-21600" windowWidth="14175" windowHeight="20985" firstSheet="1" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -294,9 +294,14 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:Q33" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:Q33" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Winter"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="0"/>
+        <filter val="3"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1204,7 +1209,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1258,7 +1263,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1312,7 +1317,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1366,7 +1371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1420,7 +1425,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1627,7 +1632,7 @@
         <v>4.8864727960722396</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1681,7 +1686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1698,7 +1703,7 @@
       <c r="E11">
         <v>10</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="3">
         <v>94059.890410960099</v>
       </c>
       <c r="G11">
@@ -1732,7 +1737,7 @@
         <v>1.7211299327173799</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1749,7 +1754,7 @@
       <c r="E12">
         <v>10</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="3">
         <v>117574.86301369801</v>
       </c>
       <c r="G12">
@@ -1783,7 +1788,7 @@
         <v>1.45968753918303</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1800,7 +1805,7 @@
       <c r="E13">
         <v>10</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="3">
         <v>141089.835616439</v>
       </c>
       <c r="G13">
@@ -1834,7 +1839,7 @@
         <v>1.2818199310829099</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1851,7 +1856,7 @@
       <c r="E14">
         <v>10</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="3">
         <v>164604.808219178</v>
       </c>
       <c r="G14">
@@ -1885,7 +1890,7 @@
         <v>1.15734642471583</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1902,7 +1907,7 @@
       <c r="E15">
         <v>10</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="3">
         <v>188119.780821792</v>
       </c>
       <c r="G15">
@@ -1936,7 +1941,7 @@
         <v>1.06438923423513</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1953,7 +1958,7 @@
       <c r="E16">
         <v>10</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="3">
         <v>211634.75342465701</v>
       </c>
       <c r="G16">
@@ -1987,7 +1992,7 @@
         <v>0.99711288227329198</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2041,7 +2046,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2095,7 +2100,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2149,7 +2154,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2203,7 +2208,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2257,7 +2262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2311,7 +2316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2365,7 +2370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2419,7 +2424,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2473,7 +2478,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2527,7 +2532,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2581,7 +2586,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -2635,7 +2640,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -2689,7 +2694,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -2743,7 +2748,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -2797,7 +2802,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -2851,7 +2856,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -2907,8 +2912,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
